--- a/templates/tpl_booking_mssnhsnoyn9v.xlsx
+++ b/templates/tpl_booking_mssnhsnoyn9v.xlsx
@@ -3129,7 +3129,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3725,6 +3725,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4939,7 +4945,12 @@
       <c r="N2" s="5"/>
     </row>
     <row r="3" customHeight="1" spans="1:14">
-      <c r="A3" s="15"/>
+      <c r="A3" s="201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{shipper.name}}
+{{shipper.address}}</t>
+        </is>
+      </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -5033,7 +5044,12 @@
       <c r="M9" s="37"/>
     </row>
     <row r="10" customHeight="1" spans="1:14">
-      <c r="A10" s="23"/>
+      <c r="A10" s="202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{consignee.name}}
+{{consignee.address}}</t>
+        </is>
+      </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>

--- a/templates/tpl_booking_mssnhsnoyn9v.xlsx
+++ b/templates/tpl_booking_mssnhsnoyn9v.xlsx
@@ -3792,58 +3792,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
-</file>
-
-<file path=xl/activeX/activeX10.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
-</file>
-
-<file path=xl/activeX/activeX11.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
-</file>
-
-<file path=xl/activeX/activeX12.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
-</file>
-
-<file path=xl/activeX/activeX13.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
-</file>
-
-<file path=xl/activeX/activeX2.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
-</file>
-
-<file path=xl/activeX/activeX3.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
-</file>
-
-<file path=xl/activeX/activeX4.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
-</file>
-
-<file path=xl/activeX/activeX5.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
-</file>
-
-<file path=xl/activeX/activeX6.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
-</file>
-
-<file path=xl/activeX/activeX7.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
-</file>
-
-<file path=xl/activeX/activeX8.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
-</file>
-
-<file path=xl/activeX/activeX9.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6375,333 +6323,6 @@
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
-  <controls>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3073" r:id="rId4">
-          <controlPr defaultSize="0" r:id="rId5">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>466725</xdr:colOff>
-                <xdr:row>16</xdr:row>
-                <xdr:rowOff>85725</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>609600</xdr:colOff>
-                <xdr:row>17</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3073" r:id="rId4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3074" r:id="rId6">
-          <controlPr defaultSize="0" r:id="rId7">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>16</xdr:row>
-                <xdr:rowOff>104775</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>142875</xdr:colOff>
-                <xdr:row>17</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3074" r:id="rId6"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3075" r:id="rId8">
-          <controlPr defaultSize="0" r:id="rId9">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>19050</xdr:colOff>
-                <xdr:row>19</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>161925</xdr:colOff>
-                <xdr:row>19</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3075" r:id="rId8"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3076" r:id="rId10">
-          <controlPr defaultSize="0" r:id="rId11">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>466725</xdr:colOff>
-                <xdr:row>19</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>609600</xdr:colOff>
-                <xdr:row>19</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3076" r:id="rId10"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3077" r:id="rId12">
-          <controlPr defaultSize="0" r:id="rId13">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>466725</xdr:colOff>
-                <xdr:row>22</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>609600</xdr:colOff>
-                <xdr:row>22</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3077" r:id="rId12"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3078" r:id="rId14">
-          <controlPr defaultSize="0" r:id="rId15">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>22</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>142875</xdr:colOff>
-                <xdr:row>22</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3078" r:id="rId14"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3079" r:id="rId16">
-          <controlPr defaultSize="0" r:id="rId17">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>9525</xdr:colOff>
-                <xdr:row>28</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>152400</xdr:colOff>
-                <xdr:row>28</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3079" r:id="rId16"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3080" r:id="rId18">
-          <controlPr defaultSize="0" r:id="rId19">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>466725</xdr:colOff>
-                <xdr:row>28</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>609600</xdr:colOff>
-                <xdr:row>28</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3080" r:id="rId18"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3081" r:id="rId20">
-          <controlPr defaultSize="0" r:id="rId21">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>25</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>142875</xdr:colOff>
-                <xdr:row>25</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3081" r:id="rId20"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3083" r:id="rId22">
-          <controlPr defaultSize="0" r:id="rId23">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>466725</xdr:colOff>
-                <xdr:row>25</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>609600</xdr:colOff>
-                <xdr:row>25</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3083" r:id="rId22"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3084" r:id="rId24">
-          <controlPr defaultSize="0" r:id="rId25">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>9525</xdr:colOff>
-                <xdr:row>25</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>152400</xdr:colOff>
-                <xdr:row>25</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3084" r:id="rId24"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3085" r:id="rId26">
-          <controlPr defaultSize="0" r:id="rId27">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>9525</xdr:colOff>
-                <xdr:row>22</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>152400</xdr:colOff>
-                <xdr:row>22</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3085" r:id="rId26"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3086" r:id="rId28">
-          <controlPr defaultSize="0" r:id="rId29">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>19</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>142875</xdr:colOff>
-                <xdr:row>19</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3086" r:id="rId28"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </controls>
 </worksheet>
 </file>
 
